--- a/Reports/Members/Chun Chieh_Activity_Report.xlsx
+++ b/Reports/Members/Chun Chieh_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,7 +497,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>

--- a/Reports/Members/Chun Chieh_Activity_Report.xlsx
+++ b/Reports/Members/Chun Chieh_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Reports/Members/Chun Chieh_Activity_Report.xlsx
+++ b/Reports/Members/Chun Chieh_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Reports/Members/Chun Chieh_Activity_Report.xlsx
+++ b/Reports/Members/Chun Chieh_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,6 +506,53 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>6/7/2026 17:27:12</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chun Chieh</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>16.44</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>25,078</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -554,10 +601,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.92</v>
+        <v>22.36</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>25078</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -624,10 +671,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.92</v>
+        <v>22.36</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>25078</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>

--- a/Reports/Members/Chun Chieh_Activity_Report.xlsx
+++ b/Reports/Members/Chun Chieh_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +555,53 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6/8/2026 8:21:19</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Chun Chieh</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>11.35</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
         </is>
       </c>
     </row>
@@ -633,7 +680,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>11.35</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -671,7 +718,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.36</v>
+        <v>33.71</v>
       </c>
       <c r="C6" t="n">
         <v>25078</v>

--- a/Reports/Members/Chun Chieh_Activity_Report.xlsx
+++ b/Reports/Members/Chun Chieh_Activity_Report.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -581,17 +581,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>17,132</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.36</v>
+        <v>33.71</v>
       </c>
       <c r="C2" t="n">
-        <v>25078</v>
+        <v>42210</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.35</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         <v>33.71</v>
       </c>
       <c r="C6" t="n">
-        <v>25078</v>
+        <v>42210</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
